--- a/test/tableToSystemArxml/WhiteTable/BcmWhiteTable.xlsx
+++ b/test/tableToSystemArxml/WhiteTable/BcmWhiteTable.xlsx
@@ -18,9 +18,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'General'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Components'!$A$1:$D$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Components'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AssemblySwConnection'!$A$1:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AssemblySwConnection'!$A$1:$D$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'AssemblySwConnection'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DelegationSwConnection'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DelegationSwConnection'!$A$1:$C$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'DelegationSwConnection'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SenderReceiverToSignal'!$A$1:$E$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'SenderReceiverToSignal'!$1:$1</definedName>
@@ -653,91 +653,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Connection</t>
+          <t>Provider SW-C</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Provider SW-C</t>
+          <t>PPort</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>PPort</t>
+          <t>Requester SW-C</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Requester SW-C</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>RPort</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>itsTUR</t>
+        </is>
+      </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>PowerMode</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>itsLIT</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>VeINP_CAN_PowerMode_sig</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>itsLIT</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>VbOUT_LIT_FLPosition_flg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
           <t>itsTUR</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>PowerMode</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>itsLIT</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>VeINP_CAN_PowerMode_sig</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>itsLIT</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>VbOUT_LIT_FLPosition_flg</t>
-        </is>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>itsTUR</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
           <t>PositionActive</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
+  <autoFilter ref="A1:D3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -749,39 +741,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Connection</t>
+          <t>Inner SW-C</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Inner SW-C</t>
+          <t>Inner Port</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Inner Port</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
           <t>Outer Port</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
+  <autoFilter ref="A1:C1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
